--- a/Data/raw/TST_Mannino_2023-10_QS/TST_2023-10_QS_metadata.xlsx
+++ b/Data/raw/TST_Mannino_2023-10_QS/TST_2023-10_QS_metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oros\Desktop\dataset_upload\TST_Mannino_2023-10_QS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4850C9CB-A961-45DC-8E24-B61496B13C87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5598DDD8-D9FB-4F83-A960-B4317CC92EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="15" windowWidth="20640" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -893,6 +893,9 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -915,9 +918,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -925,21 +925,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -1513,55 +1499,55 @@
     <row r="1" spans="1:41" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11"/>
       <c r="B1" s="11"/>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
       <c r="R1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="S1" s="27" t="s">
+      <c r="S1" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="27"/>
-      <c r="Z1" s="27"/>
-      <c r="AA1" s="27"/>
-      <c r="AB1" s="27"/>
-      <c r="AC1" s="27"/>
-      <c r="AD1" s="27"/>
-      <c r="AE1" s="27"/>
-      <c r="AF1" s="27"/>
-      <c r="AG1" s="27"/>
-      <c r="AH1" s="27"/>
-      <c r="AI1" s="27"/>
-      <c r="AJ1" s="27"/>
-      <c r="AK1" s="27"/>
-      <c r="AL1" s="25" t="s">
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="28"/>
+      <c r="AJ1" s="28"/>
+      <c r="AK1" s="28"/>
+      <c r="AL1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="AM1" s="25"/>
-      <c r="AN1" s="22" t="s">
+      <c r="AM1" s="26"/>
+      <c r="AN1" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AO1" s="23"/>
+      <c r="AO1" s="24"/>
     </row>
     <row r="2" spans="1:41" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
@@ -1720,7 +1706,7 @@
       <c r="O3" s="13"/>
       <c r="P3" s="13"/>
       <c r="Q3" s="13"/>
-      <c r="R3" s="30" t="s">
+      <c r="R3" s="22" t="s">
         <v>156</v>
       </c>
       <c r="S3" s="12" t="s">
@@ -2101,14 +2087,14 @@
       <c r="S7" s="1"/>
     </row>
     <row r="8" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="B8" s="24"/>
+      <c r="B8" s="25"/>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A9" s="24"/>
-      <c r="B9" s="24"/>
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -2120,32 +2106,32 @@
     <mergeCell ref="S1:AK1"/>
   </mergeCells>
   <conditionalFormatting sqref="G3">
-    <cfRule type="expression" dxfId="7" priority="6">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>F3="QS"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3 O3 AN3:AO3">
-    <cfRule type="expression" dxfId="6" priority="9">
+    <cfRule type="expression" dxfId="4" priority="9">
       <formula>$F$3="FA"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I3">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>F3="OT"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J3 P3">
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>I3="Other"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K3">
-    <cfRule type="expression" dxfId="3" priority="7">
+    <cfRule type="expression" dxfId="1" priority="7">
       <formula>OR(G3="fracture", H3="fracture")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U3">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>S3="Other polymers"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2228,29 +2214,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="29" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="27" t="s">
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="25" t="s">
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="K1" s="25"/>
-      <c r="L1" s="28" t="s">
+      <c r="K1" s="26"/>
+      <c r="L1" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="M1" s="28"/>
+      <c r="M1" s="29"/>
     </row>
     <row r="2" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
@@ -2305,10 +2291,10 @@
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
       <c r="G3" s="12">
+        <v>13.11</v>
+      </c>
+      <c r="H3" s="12">
         <v>3.18</v>
-      </c>
-      <c r="H3" s="12">
-        <v>13.11</v>
       </c>
       <c r="I3" s="13"/>
       <c r="J3" s="19"/>
@@ -2328,10 +2314,10 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
       <c r="G4" s="12">
+        <v>12.95</v>
+      </c>
+      <c r="H4" s="12">
         <v>3.24</v>
-      </c>
-      <c r="H4" s="12">
-        <v>12.95</v>
       </c>
       <c r="I4" s="13"/>
       <c r="J4" s="19"/>
@@ -2351,10 +2337,10 @@
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="12">
+        <v>12.93</v>
+      </c>
+      <c r="H5" s="12">
         <v>3.24</v>
-      </c>
-      <c r="H5" s="12">
-        <v>12.93</v>
       </c>
       <c r="I5" s="13"/>
       <c r="J5" s="19"/>
@@ -2374,10 +2360,10 @@
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
       <c r="G6" s="12">
+        <v>12.95</v>
+      </c>
+      <c r="H6" s="12">
         <v>3.4</v>
-      </c>
-      <c r="H6" s="12">
-        <v>12.95</v>
       </c>
       <c r="I6" s="13"/>
       <c r="J6" s="19"/>

--- a/Data/raw/TST_Mannino_2023-10_QS/TST_2023-10_QS_metadata.xlsx
+++ b/Data/raw/TST_Mannino_2023-10_QS/TST_2023-10_QS_metadata.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oros\Desktop\dataset_upload\TST_Mannino_2023-10_QS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5598DDD8-D9FB-4F83-A960-B4317CC92EDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA7FFA8-9936-4EF1-9B24-37D2C44D5C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="15" windowWidth="20640" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="15" windowWidth="20640" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Experiment" sheetId="1" r:id="rId1"/>
@@ -482,9 +482,6 @@
     <t>Hardener</t>
   </si>
   <si>
-    <t>Material</t>
-  </si>
-  <si>
     <t>Sequential number</t>
   </si>
   <si>
@@ -569,9 +566,6 @@
     <t>Rate used for testing, if Control mode is LC then it's loading rate, if you have selected DC is displacement rate and the same for SC . If Experiment type is FA you can skip this and add frequency</t>
   </si>
   <si>
-    <t>CCLab</t>
-  </si>
-  <si>
     <t>Filippo Mannino</t>
   </si>
   <si>
@@ -584,9 +578,6 @@
     <t>Type I</t>
   </si>
   <si>
-    <t>Sikadur-330, epoxy resin</t>
-  </si>
-  <si>
     <t>T1-DC-1</t>
   </si>
   <si>
@@ -597,6 +588,15 @@
   </si>
   <si>
     <t>T1-DC-4</t>
+  </si>
+  <si>
+    <t>Fiber Material</t>
+  </si>
+  <si>
+    <t>Epoxy Sikadur-330</t>
+  </si>
+  <si>
+    <t>GR-MeC</t>
   </si>
 </sst>
 </file>
@@ -1053,23 +1053,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>308162</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>793751</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>231589</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>104588</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>1621745</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>171775</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>1099716</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>53233</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
+        <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC0C11FC-D7EF-49B6-9CF8-E8BD18A71247}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20CE92EF-8F08-48E3-898C-71B0BBCE3345}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1085,8 +1085,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23429633" y="3585883"/>
-          <a:ext cx="6096851" cy="3391373"/>
+          <a:off x="36912177" y="3765176"/>
+          <a:ext cx="5679186" cy="2167410"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1520,7 +1520,7 @@
         <v>1</v>
       </c>
       <c r="S1" s="28" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="T1" s="28"/>
       <c r="U1" s="28"/>
@@ -1612,7 +1612,7 @@
         <v>110</v>
       </c>
       <c r="V2" s="11" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="W2" s="11" t="s">
         <v>111</v>
@@ -1678,13 +1678,13 @@
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>153</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>155</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>45</v>
@@ -1707,20 +1707,20 @@
       <c r="P3" s="13"/>
       <c r="Q3" s="13"/>
       <c r="R3" s="22" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="S3" s="12" t="s">
         <v>85</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="U3" s="14"/>
       <c r="V3" s="15"/>
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
       <c r="Y3" s="13" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="Z3" s="13"/>
       <c r="AA3" s="13"/>
@@ -1847,7 +1847,7 @@
         <v>24</v>
       </c>
       <c r="AO4" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:41" ht="78" x14ac:dyDescent="0.3">
@@ -1898,7 +1898,7 @@
         <v>68</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R5" s="6" t="s">
         <v>19</v>
@@ -1999,16 +1999,16 @@
         <v>75</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O6" s="9" t="s">
         <v>11</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="R6" s="9" t="s">
         <v>12</v>
@@ -2077,10 +2077,10 @@
         <v>16</v>
       </c>
       <c r="AN6" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AO6" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.3">
@@ -2088,7 +2088,7 @@
     </row>
     <row r="8" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B8" s="25"/>
     </row>
@@ -2240,43 +2240,43 @@
     </row>
     <row r="2" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="C2" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="D2" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="E2" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="F2" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="G2" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="H2" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="I2" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="J2" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="K2" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="L2" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="M2" s="11" t="s">
         <v>142</v>
-      </c>
-      <c r="M2" s="11" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -2284,7 +2284,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
@@ -2307,7 +2307,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -2330,7 +2330,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
@@ -2353,7 +2353,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>

--- a/Data/raw/TST_Mannino_2023-10_QS/TST_2023-10_QS_metadata.xlsx
+++ b/Data/raw/TST_Mannino_2023-10_QS/TST_2023-10_QS_metadata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oros\Desktop\dataset_upload\TST_Mannino_2023-10_QS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA7FFA8-9936-4EF1-9B24-37D2C44D5C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{251B7409-F854-4E6E-A9BF-05121122AFBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="15" windowWidth="20640" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="15" windowWidth="20640" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Experiment" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="165">
   <si>
     <t>General</t>
   </si>
@@ -597,6 +597,12 @@
   </si>
   <si>
     <t>GR-MeC</t>
+  </si>
+  <si>
+    <t>L'</t>
+  </si>
+  <si>
+    <t>t</t>
   </si>
 </sst>
 </file>
@@ -726,7 +732,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -827,12 +833,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -918,6 +935,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2195,7 +2221,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.33203125" style="8" customWidth="1"/>
@@ -2206,14 +2232,14 @@
     <col min="6" max="6" width="19.109375" style="8" customWidth="1"/>
     <col min="7" max="7" width="19.88671875" style="8" customWidth="1"/>
     <col min="8" max="8" width="20.5546875" style="8" customWidth="1"/>
-    <col min="9" max="9" width="20.109375" style="8" customWidth="1"/>
-    <col min="10" max="11" width="15.6640625" style="8" customWidth="1"/>
-    <col min="12" max="12" width="21.88671875" style="8" customWidth="1"/>
-    <col min="13" max="13" width="20" style="8" customWidth="1"/>
-    <col min="14" max="16384" width="8.6640625" style="8"/>
+    <col min="9" max="11" width="20.109375" style="8" customWidth="1"/>
+    <col min="12" max="13" width="15.6640625" style="8" customWidth="1"/>
+    <col min="14" max="14" width="21.88671875" style="8" customWidth="1"/>
+    <col min="15" max="15" width="20" style="8" customWidth="1"/>
+    <col min="16" max="16384" width="8.6640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
         <v>101</v>
       </c>
@@ -2223,22 +2249,24 @@
       </c>
       <c r="D1" s="30"/>
       <c r="E1" s="30"/>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="26" t="s">
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="K1" s="26"/>
-      <c r="L1" s="29" t="s">
+      <c r="M1" s="26"/>
+      <c r="N1" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="M1" s="29"/>
-    </row>
-    <row r="2" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O1" s="29"/>
+    </row>
+    <row r="2" spans="1:15" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>130</v>
       </c>
@@ -2267,19 +2295,25 @@
         <v>138</v>
       </c>
       <c r="J2" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="L2" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="M2" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="O2" s="11" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="12">
         <v>1</v>
       </c>
@@ -2297,12 +2331,14 @@
         <v>3.18</v>
       </c>
       <c r="I3" s="13"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
         <v>2</v>
       </c>
@@ -2320,12 +2356,14 @@
         <v>3.24</v>
       </c>
       <c r="I4" s="13"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
         <v>3</v>
       </c>
@@ -2343,12 +2381,14 @@
         <v>3.24</v>
       </c>
       <c r="I5" s="13"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="12">
         <v>4</v>
       </c>
@@ -2366,66 +2406,68 @@
         <v>3.4</v>
       </c>
       <c r="I6" s="13"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="D16" s="1"/>
@@ -2470,11 +2512,11 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="5">
-    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="N1:O1"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="F1:K1"/>
   </mergeCells>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
